--- a/templates/HR_Ops_Template.xlsx
+++ b/templates/HR_Ops_Template.xlsx
@@ -11,6 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diversity" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Attrition &amp; Retention" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRF" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Learning &amp; Development" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -130,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -173,6 +175,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2470,4 +2481,781 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>HR Operations — Learning &amp; Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>May 2026 · Yellow cells = input · Training programs conducted this month</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>TRAININGS CONDUCTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Training Program</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>No. of Participants</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Expense (₱)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Training Evaluation (1–5)</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>LEM Score</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="17" t="n"/>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="18" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="17" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="17" t="n"/>
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="10" t="n"/>
+      <c r="D6" s="18" t="n"/>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="17" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="17" t="n"/>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="18" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="10" t="n"/>
+      <c r="G7" s="17" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="17" t="n"/>
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="18" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="17" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="17" t="n"/>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="18" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="17" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="17" t="n"/>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="18" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="17" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="17" t="n"/>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="18" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="17" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="17" t="n"/>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="17" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="17" t="n"/>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="18" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="17" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="17" t="n"/>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="18" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="17" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>DISTRIBUTION OF TRAINING ATTENDEES</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>CSI</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>PPC</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>AMICI</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>CSPIC</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>PTMSI</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>PTMSI SB</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>EPICS</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>PSEFI</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>SKILLS</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>SKL COOP</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>PSI</t>
+        </is>
+      </c>
+      <c r="P17" s="4" t="inlineStr">
+        <is>
+          <t>APODIS</t>
+        </is>
+      </c>
+      <c r="Q17" s="4" t="inlineStr">
+        <is>
+          <t>MLG</t>
+        </is>
+      </c>
+      <c r="R17" s="4" t="inlineStr">
+        <is>
+          <t>THAM</t>
+        </is>
+      </c>
+      <c r="S17" s="4" t="inlineStr">
+        <is>
+          <t>SLM</t>
+        </is>
+      </c>
+      <c r="T17" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>No. of Attendees</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="10" t="n"/>
+      <c r="H18" s="10" t="n"/>
+      <c r="I18" s="10" t="n"/>
+      <c r="J18" s="10" t="n"/>
+      <c r="K18" s="10" t="n"/>
+      <c r="L18" s="10" t="n"/>
+      <c r="M18" s="10" t="n"/>
+      <c r="N18" s="10" t="n"/>
+      <c r="O18" s="10" t="n"/>
+      <c r="P18" s="10" t="n"/>
+      <c r="Q18" s="10" t="n"/>
+      <c r="R18" s="10" t="n"/>
+      <c r="S18" s="10" t="n"/>
+      <c r="T18" s="11">
+        <f>SUM(B18:S18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>% vs Headcount</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="10" t="n"/>
+      <c r="H19" s="10" t="n"/>
+      <c r="I19" s="10" t="n"/>
+      <c r="J19" s="10" t="n"/>
+      <c r="K19" s="10" t="n"/>
+      <c r="L19" s="10" t="n"/>
+      <c r="M19" s="10" t="n"/>
+      <c r="N19" s="10" t="n"/>
+      <c r="O19" s="10" t="n"/>
+      <c r="P19" s="10" t="n"/>
+      <c r="Q19" s="10" t="n"/>
+      <c r="R19" s="10" t="n"/>
+      <c r="S19" s="10" t="n"/>
+      <c r="T19" s="13" t="n"/>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>LEM = (Avg Post-test Score – Avg Pre-test Score) ÷ Total Test Score   |   Training Eval rated 1–5 by participants</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A21:T21"/>
+    <mergeCell ref="A16:T16"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>HR Operations — Performance</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>May 2026 · QoNH = Quality of New Hire · Movement: Probationary → Regular</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>CSI</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>PPC</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>AMICI</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>CSPIC</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>PTMSI</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>PSEFI</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>SKILLS</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>PSI</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>MLG</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>THAM</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>SLM</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Quality of New Hire (QoNH)</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="7" t="n"/>
+      <c r="H4" s="7" t="n"/>
+      <c r="I4" s="7" t="n"/>
+      <c r="J4" s="7" t="n"/>
+      <c r="K4" s="7" t="n"/>
+      <c r="L4" s="7" t="n"/>
+      <c r="M4" s="7" t="n"/>
+      <c r="N4" s="7" t="n"/>
+      <c r="O4" s="7" t="n"/>
+      <c r="P4" s="8" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Movement (Prob → Regular)</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n"/>
+      <c r="I5" s="10" t="n"/>
+      <c r="J5" s="10" t="n"/>
+      <c r="K5" s="10" t="n"/>
+      <c r="L5" s="10" t="n"/>
+      <c r="M5" s="10" t="n"/>
+      <c r="N5" s="10" t="n"/>
+      <c r="O5" s="10" t="n"/>
+      <c r="P5" s="11">
+        <f>SUM(B5:O5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Probationary</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="10" t="n"/>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="10" t="n"/>
+      <c r="I6" s="10" t="n"/>
+      <c r="J6" s="10" t="n"/>
+      <c r="K6" s="10" t="n"/>
+      <c r="L6" s="10" t="n"/>
+      <c r="M6" s="10" t="n"/>
+      <c r="N6" s="10" t="n"/>
+      <c r="O6" s="10" t="n"/>
+      <c r="P6" s="11">
+        <f>SUM(B6:O6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="10" t="n"/>
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="10" t="n"/>
+      <c r="I7" s="10" t="n"/>
+      <c r="J7" s="10" t="n"/>
+      <c r="K7" s="10" t="n"/>
+      <c r="L7" s="10" t="n"/>
+      <c r="M7" s="10" t="n"/>
+      <c r="N7" s="10" t="n"/>
+      <c r="O7" s="10" t="n"/>
+      <c r="P7" s="11">
+        <f>SUM(B7:O7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Annual Performance Appraisal</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
+      <c r="J8" s="7" t="n"/>
+      <c r="K8" s="7" t="n"/>
+      <c r="L8" s="7" t="n"/>
+      <c r="M8" s="7" t="n"/>
+      <c r="N8" s="7" t="n"/>
+      <c r="O8" s="7" t="n"/>
+      <c r="P8" s="8" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Total Employees for Appraisal</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n"/>
+      <c r="I9" s="10" t="n"/>
+      <c r="J9" s="10" t="n"/>
+      <c r="K9" s="10" t="n"/>
+      <c r="L9" s="10" t="n"/>
+      <c r="M9" s="10" t="n"/>
+      <c r="N9" s="10" t="n"/>
+      <c r="O9" s="10" t="n"/>
+      <c r="P9" s="11">
+        <f>SUM(B9:O9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="10" t="n"/>
+      <c r="I10" s="10" t="n"/>
+      <c r="J10" s="10" t="n"/>
+      <c r="K10" s="10" t="n"/>
+      <c r="L10" s="10" t="n"/>
+      <c r="M10" s="10" t="n"/>
+      <c r="N10" s="10" t="n"/>
+      <c r="O10" s="10" t="n"/>
+      <c r="P10" s="11">
+        <f>SUM(B10:O10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="10" t="n"/>
+      <c r="H11" s="10" t="n"/>
+      <c r="I11" s="10" t="n"/>
+      <c r="J11" s="10" t="n"/>
+      <c r="K11" s="10" t="n"/>
+      <c r="L11" s="10" t="n"/>
+      <c r="M11" s="10" t="n"/>
+      <c r="N11" s="10" t="n"/>
+      <c r="O11" s="10" t="n"/>
+      <c r="P11" s="11">
+        <f>SUM(B11:O11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Completion Rate (%)</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="10" t="n"/>
+      <c r="H12" s="10" t="n"/>
+      <c r="I12" s="10" t="n"/>
+      <c r="J12" s="10" t="n"/>
+      <c r="K12" s="10" t="n"/>
+      <c r="L12" s="10" t="n"/>
+      <c r="M12" s="10" t="n"/>
+      <c r="N12" s="10" t="n"/>
+      <c r="O12" s="10" t="n"/>
+      <c r="P12" s="11">
+        <f>SUM(B12:O12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Performance Improvement Plan</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="7" t="n"/>
+      <c r="I13" s="7" t="n"/>
+      <c r="J13" s="7" t="n"/>
+      <c r="K13" s="7" t="n"/>
+      <c r="L13" s="7" t="n"/>
+      <c r="M13" s="7" t="n"/>
+      <c r="N13" s="7" t="n"/>
+      <c r="O13" s="7" t="n"/>
+      <c r="P13" s="8" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Employees on PIP</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="10" t="n"/>
+      <c r="H14" s="10" t="n"/>
+      <c r="I14" s="10" t="n"/>
+      <c r="J14" s="10" t="n"/>
+      <c r="K14" s="10" t="n"/>
+      <c r="L14" s="10" t="n"/>
+      <c r="M14" s="10" t="n"/>
+      <c r="N14" s="10" t="n"/>
+      <c r="O14" s="10" t="n"/>
+      <c r="P14" s="11">
+        <f>SUM(B14:O14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>PIP Completed</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="10" t="n"/>
+      <c r="H15" s="10" t="n"/>
+      <c r="I15" s="10" t="n"/>
+      <c r="J15" s="10" t="n"/>
+      <c r="K15" s="10" t="n"/>
+      <c r="L15" s="10" t="n"/>
+      <c r="M15" s="10" t="n"/>
+      <c r="N15" s="10" t="n"/>
+      <c r="O15" s="10" t="n"/>
+      <c r="P15" s="11">
+        <f>SUM(B15:O15)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A2:P2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>